--- a/stories/arbres/TREE-SEC-009.xlsx
+++ b/stories/arbres/TREE-SEC-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Nora est dans le jardin avec Papa. Papa est l'accompagnant. Nora reste avec l'accompagnant. Ses pieds restent à côté de Papa. Sa main tient la main de Papa. Maman arrose les fleurs.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pousse le petit train. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
     </row>
@@ -2005,6 +2042,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2193,6 +2235,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Tom. Un oiseau chante. Tom vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2599,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2770,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2937,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3108,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le bois du train claque. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3275,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3446,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Une abeille passe. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3613,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3784,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Léa. L'arrosoir glouglou. Léa vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3883,6 +3975,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4049,6 +4146,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le bois du train claque. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4211,6 +4313,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4377,6 +4484,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Une abeille passe. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4539,6 +4651,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4705,6 +4822,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. L'herbe est fraîche. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4867,6 +4989,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5033,6 +5160,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Sami. Le vent est doux. Sami vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5219,6 +5351,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5385,6 +5522,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Une abeille passe. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5547,6 +5689,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5713,6 +5860,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. L'herbe est fraîche. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5875,6 +6027,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6041,6 +6198,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6203,6 +6365,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6369,6 +6536,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pousse le petit bus. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6549,6 +6721,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
     </row>
@@ -6721,6 +6898,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6909,6 +7091,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7077,6 +7264,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Tom. Le bois du train claque. Tom vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,6 +7455,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7429,6 +7626,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le bois du train claque. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7591,6 +7793,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7757,6 +7964,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Une abeille passe. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7919,6 +8131,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8085,6 +8302,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. L'herbe est fraîche. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8247,6 +8469,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8413,6 +8640,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Léa. Une abeille passe. Léa vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8599,6 +8831,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8765,6 +9002,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Une abeille passe. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8927,6 +9169,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9093,6 +9340,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. L'herbe est fraîche. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9255,6 +9507,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9421,6 +9678,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9583,6 +9845,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9749,6 +10016,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Sami. L'herbe est fraîche. Sami vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9935,6 +10207,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10101,6 +10378,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. L'herbe est fraîche. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10263,6 +10545,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10429,6 +10716,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un oiseau chante. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10591,6 +10883,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10757,6 +11054,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. L'arrosoir glouglou. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10919,6 +11221,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11085,6 +11392,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pousse la petite voiture. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11265,6 +11577,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
     </row>
@@ -11437,6 +11754,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11625,6 +11947,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11793,6 +12120,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Tom. Un oiseau chante. Tom vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11979,6 +12311,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12145,6 +12482,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Une abeille passe. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12307,6 +12649,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12473,6 +12820,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. L'herbe est fraîche. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12635,6 +12987,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12801,6 +13158,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12963,6 +13325,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13129,6 +13496,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Léa. L'arrosoir glouglou. Léa vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13315,6 +13687,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13481,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. L'herbe est fraîche. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13643,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13809,6 +14196,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un oiseau chante. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13971,6 +14363,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14137,6 +14534,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. L'arrosoir glouglou. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14299,6 +14701,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14465,6 +14872,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi Sami. Le vent est doux. Sami vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14651,6 +15063,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14817,6 +15234,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un oiseau chante. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14979,6 +15401,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15145,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. L'arrosoir glouglou. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15307,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15473,6 +15910,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15635,6 +16077,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15653,7 +16100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15684,6 +16131,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-009.xlsx
+++ b/stories/arbres/TREE-SEC-009.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Nora est dans le jardin avec Papa. Papa est l'accompagnant. Nora reste avec l'accompagnant. Ses pieds restent à côté de Papa. Sa main tient la main de Papa. Maman arrose les fleurs.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Nora pousse le petit train. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2047,6 +2056,7 @@
           <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Nora a choisi Tom. Un oiseau chante. Tom vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2604,6 +2616,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2775,6 +2788,7 @@
           <t>narrateur|C'est le matin. Le vent est doux. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2942,6 +2956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3113,6 +3128,7 @@
           <t>narrateur|C'est après la sieste. Le bois du train claque. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3280,6 +3296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3451,6 +3468,7 @@
           <t>narrateur|C'est le soir. Une abeille passe. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3618,6 +3636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3789,6 +3808,7 @@
           <t>narrateur|Nora a choisi Léa. L'arrosoir glouglou. Léa vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3980,6 +4000,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4151,6 +4172,7 @@
           <t>narrateur|C'est le matin. Le bois du train claque. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4318,6 +4340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4489,6 +4512,7 @@
           <t>narrateur|C'est après la sieste. Une abeille passe. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4656,6 +4680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4827,6 +4852,7 @@
           <t>narrateur|C'est le soir. L'herbe est fraîche. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4994,6 +5020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5165,6 +5192,7 @@
           <t>narrateur|Nora a choisi Sami. Le vent est doux. Sami vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5356,6 +5384,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5527,6 +5556,7 @@
           <t>narrateur|C'est le matin. Une abeille passe. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5694,6 +5724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5865,6 +5896,7 @@
           <t>narrateur|C'est après la sieste. L'herbe est fraîche. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6032,6 +6064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6203,6 +6236,7 @@
           <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6370,6 +6404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6541,6 +6576,7 @@
           <t>narrateur|Nora pousse le petit bus. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6728,6 +6764,7 @@
           <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6903,6 +6940,7 @@
           <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7098,6 +7136,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7269,6 +7308,7 @@
           <t>narrateur|Nora a choisi Tom. Le bois du train claque. Tom vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7460,6 +7500,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7631,6 +7672,7 @@
           <t>narrateur|C'est le matin. Le bois du train claque. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7798,6 +7840,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7969,6 +8012,7 @@
           <t>narrateur|C'est après la sieste. Une abeille passe. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8136,6 +8180,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8307,6 +8352,7 @@
           <t>narrateur|C'est le soir. L'herbe est fraîche. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8474,6 +8520,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8645,6 +8692,7 @@
           <t>narrateur|Nora a choisi Léa. Une abeille passe. Léa vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8836,6 +8884,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9007,6 +9056,7 @@
           <t>narrateur|C'est le matin. Une abeille passe. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9174,6 +9224,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9345,6 +9396,7 @@
           <t>narrateur|C'est après la sieste. L'herbe est fraîche. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9512,6 +9564,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9683,6 +9736,7 @@
           <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9850,6 +9904,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10021,6 +10076,7 @@
           <t>narrateur|Nora a choisi Sami. L'herbe est fraîche. Sami vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10212,6 +10268,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10383,6 +10440,7 @@
           <t>narrateur|C'est le matin. L'herbe est fraîche. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10550,6 +10608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10721,6 +10780,7 @@
           <t>narrateur|C'est après la sieste. Un oiseau chante. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10888,6 +10948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11059,6 +11120,7 @@
           <t>narrateur|C'est le soir. L'arrosoir glouglou. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11226,6 +11288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11397,6 +11460,7 @@
           <t>narrateur|Nora pousse la petite voiture. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11584,6 +11648,7 @@
           <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11759,6 +11824,7 @@
           <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11954,6 +12020,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12125,6 +12192,7 @@
           <t>narrateur|Nora a choisi Tom. Un oiseau chante. Tom vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12316,6 +12384,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12487,6 +12556,7 @@
           <t>narrateur|C'est le matin. Une abeille passe. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12654,6 +12724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12825,6 +12896,7 @@
           <t>narrateur|C'est après la sieste. L'herbe est fraîche. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12992,6 +13064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13163,6 +13236,7 @@
           <t>narrateur|C'est le soir. Un oiseau chante. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13330,6 +13404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13501,6 +13576,7 @@
           <t>narrateur|Nora a choisi Léa. L'arrosoir glouglou. Léa vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13692,6 +13768,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13863,6 +13940,7 @@
           <t>narrateur|C'est le matin. L'herbe est fraîche. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14030,6 +14108,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14201,6 +14280,7 @@
           <t>narrateur|C'est après la sieste. Un oiseau chante. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14368,6 +14448,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14539,6 +14620,7 @@
           <t>narrateur|C'est le soir. L'arrosoir glouglou. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14706,6 +14788,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14877,6 +14960,7 @@
           <t>narrateur|Nora a choisi Sami. Le vent est doux. Sami vient. Nora reste avec l'accompagnant, près de Papa. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15068,6 +15152,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15239,6 +15324,7 @@
           <t>narrateur|C'est le matin. Un oiseau chante. C'est le matin. Nora reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15406,6 +15492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15577,6 +15664,7 @@
           <t>narrateur|C'est après la sieste. L'arrosoir glouglou. C'est après la sieste. Nora reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15744,6 +15832,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15915,6 +16004,7 @@
           <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. Nora reste à côté de Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Nora dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16082,6 +16172,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16100,7 +16191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16138,6 +16229,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16339,6 +16444,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
